--- a/Supplementary Information/S9 qPCR Primer-Probe Panel.xlsx
+++ b/Supplementary Information/S9 qPCR Primer-Probe Panel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\devin\Desktop\paper\claude\metadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\devin\Desktop\rrms\Supplementary Information\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C768AE-CADF-48B7-9D4D-74D00B34907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0EDF82-0AD8-4AC9-9BC6-778A6CF2B9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2287" yWindow="720" windowWidth="26183" windowHeight="14407" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="qPCR Primer-Probe Panel" sheetId="1" r:id="rId1"/>
@@ -227,18 +227,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8.5"/>
-      <color rgb="FF000000"/>
-      <name val="Consolas"/>
     </font>
     <font>
       <b/>
@@ -255,14 +250,13 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -329,36 +323,36 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -663,312 +657,313 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16" style="6" customWidth="1"/>
-    <col min="2" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="38" customWidth="1"/>
-    <col min="5" max="5" width="13" style="6" customWidth="1"/>
-    <col min="6" max="6" width="26" style="6" customWidth="1"/>
+    <col min="1" max="1" width="16" style="9" customWidth="1"/>
+    <col min="2" max="3" width="32" style="9" customWidth="1"/>
+    <col min="4" max="4" width="38" style="9" customWidth="1"/>
+    <col min="5" max="5" width="13" style="9" customWidth="1"/>
+    <col min="6" max="6" width="26" style="9" customWidth="1"/>
+    <col min="7" max="16384" width="9.06640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:6" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:6" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:6" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:6" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:6" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:6" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:6" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:6" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:6" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:6" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:6" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:6" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:6" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:6" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:6" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="7" t="s">
         <v>11</v>
       </c>
     </row>
